--- a/docs/crc.xlsx
+++ b/docs/crc.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Зберігає номер, оригінал і переклад сегмента.</t>
+          <t>Зберігає номер, оригінал, переклад і стан перевірки сегмента.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
